--- a/oofem-csharp/oofem-examples/structures/guide-example.xlsx
+++ b/oofem-csharp/oofem-examples/structures/guide-example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maba/sciebo/lehrveranstaltungen/oofem/oofem-implementation-guide/oofem-csharp/oofem-examples/structures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE7635C-8508-F947-AE09-144B332A8248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C0E7F9-97D5-0A49-AFE3-C54E42CD4F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{C0BE1888-9F5D-0E40-A24C-68FF3AAF0F8A}"/>
   </bookViews>
@@ -79,12 +79,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -108,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -119,6 +126,15 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,22 +494,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -549,70 +565,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DE60AA-B04E-EA48-AB66-6293ACB99B69}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="2"/>
-    <col min="3" max="3" width="16.83203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="3"/>
-    <col min="5" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="14" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="3" customWidth="1"/>
+    <col min="3" max="4" width="6.5" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
+        <v>10000000000</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1E-4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
         <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>10000000000</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1E-4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2">
+        <v>10000000000</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1E-4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
         <v>2</v>
-      </c>
-      <c r="C3" s="2">
-        <v>10000000000</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1E-4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
+        <v>10000000000</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1E-4</v>
+      </c>
+      <c r="C4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="D4" s="2">
         <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>10000000000</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1E-4</v>
       </c>
     </row>
   </sheetData>
